--- a/Organizacion_Proyecto/Calendario_actividades/Calendario de actividades.xlsx
+++ b/Organizacion_Proyecto/Calendario_actividades/Calendario de actividades.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elies\Documents\GitHub\integradoraTeampoderoso\PropuestaProyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elies\Documents\GitHub\integradoraTeampoderoso\Organizacion_Proyecto\Calendario_actividades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F155780-D1A5-442A-BBAA-31B1D10B2E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2899B3-2E19-49B5-A43C-8E9B4ACBA959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30A5C19A-5DFA-4927-AC28-1A5B7C8ACF0F}"/>
   </bookViews>
@@ -381,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -401,6 +401,117 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -410,123 +521,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -861,76 +862,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
     </row>
     <row r="2" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="47">
+      <c r="B2" s="17">
         <v>2025</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
     </row>
     <row r="3" spans="2:17" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46" t="s">
+      <c r="C3" s="16"/>
+      <c r="D3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46" t="s">
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46" t="s">
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="46"/>
+      <c r="Q3" s="16"/>
     </row>
     <row r="4" spans="2:17" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
@@ -975,10 +976,10 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="37"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -995,10 +996,10 @@
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="19"/>
+      <c r="C6" s="12"/>
       <c r="D6" s="9"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1015,8 +1016,8 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="1"/>
@@ -1033,10 +1034,10 @@
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="12"/>
       <c r="D8" s="1"/>
       <c r="E8" s="9"/>
       <c r="F8" s="1"/>
@@ -1053,8 +1054,8 @@
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
       <c r="D9" s="1"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -1071,10 +1072,10 @@
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="19"/>
+      <c r="C10" s="12"/>
       <c r="D10" s="1"/>
       <c r="E10" s="9"/>
       <c r="F10" s="1"/>
@@ -1091,11 +1092,11 @@
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1109,10 +1110,10 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="12"/>
       <c r="D12" s="1"/>
       <c r="E12" s="9"/>
       <c r="F12" s="1"/>
@@ -1129,8 +1130,8 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="1"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -1147,10 +1148,10 @@
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="1"/>
       <c r="E14" s="9"/>
       <c r="F14" s="1"/>
@@ -1167,8 +1168,8 @@
       <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
       <c r="D15" s="1"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -1185,10 +1186,10 @@
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="12"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="9"/>
@@ -1205,8 +1206,8 @@
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="10"/>
@@ -1223,10 +1224,10 @@
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="9"/>
@@ -1243,8 +1244,8 @@
       <c r="Q18" s="1"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="10"/>
@@ -1261,10 +1262,10 @@
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="12"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1281,8 +1282,8 @@
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="20"/>
-      <c r="C21" s="21"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1299,10 +1300,10 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="37"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -1319,8 +1320,8 @@
       <c r="Q22" s="22"/>
     </row>
     <row r="23" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
@@ -1337,10 +1338,10 @@
       <c r="Q23" s="23"/>
     </row>
     <row r="24" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="19"/>
+      <c r="C24" s="12"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="9"/>
@@ -1357,8 +1358,8 @@
       <c r="Q24" s="4"/>
     </row>
     <row r="25" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="20"/>
-      <c r="C25" s="21"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="10"/>
@@ -1375,10 +1376,10 @@
       <c r="Q25" s="1"/>
     </row>
     <row r="26" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="19"/>
+      <c r="C26" s="12"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="9"/>
@@ -1395,8 +1396,8 @@
       <c r="Q26" s="1"/>
     </row>
     <row r="27" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="20"/>
-      <c r="C27" s="21"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="10"/>
@@ -1413,10 +1414,10 @@
       <c r="Q27" s="1"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="19"/>
+      <c r="C28" s="12"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="9"/>
@@ -1433,8 +1434,8 @@
       <c r="Q28" s="1"/>
     </row>
     <row r="29" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="20"/>
-      <c r="C29" s="21"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="10"/>
@@ -1451,10 +1452,10 @@
       <c r="Q29" s="1"/>
     </row>
     <row r="30" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="33"/>
+      <c r="C30" s="39"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="9"/>
@@ -1471,8 +1472,8 @@
       <c r="Q30" s="1"/>
     </row>
     <row r="31" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="34"/>
-      <c r="C31" s="35"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="10"/>
@@ -1489,10 +1490,10 @@
       <c r="Q31" s="1"/>
     </row>
     <row r="32" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="33"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="9"/>
@@ -1509,8 +1510,8 @@
       <c r="Q32" s="1"/>
     </row>
     <row r="33" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="34"/>
-      <c r="C33" s="35"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="10"/>
@@ -1527,48 +1528,48 @@
       <c r="Q33" s="1"/>
     </row>
     <row r="34" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
       <c r="F34" s="22"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="38"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
     </row>
     <row r="35" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
       <c r="F35" s="23"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="38"/>
-      <c r="L35" s="38"/>
-      <c r="M35" s="38"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="38"/>
-      <c r="P35" s="38"/>
-      <c r="Q35" s="38"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
     </row>
     <row r="36" spans="2:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="37"/>
+      <c r="C36" s="19"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -1585,10 +1586,10 @@
       <c r="Q36" s="1"/>
     </row>
     <row r="37" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="19"/>
+      <c r="C37" s="12"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -1605,8 +1606,8 @@
       <c r="Q37" s="1"/>
     </row>
     <row r="38" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="20"/>
-      <c r="C38" s="21"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -1623,10 +1624,10 @@
       <c r="Q38" s="1"/>
     </row>
     <row r="39" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="25"/>
+      <c r="C39" s="52"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -1643,10 +1644,10 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="27"/>
+      <c r="C40" s="34"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -1663,8 +1664,8 @@
       <c r="Q40" s="8"/>
     </row>
     <row r="41" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="36"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -1681,10 +1682,10 @@
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="27"/>
+      <c r="C42" s="34"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -1701,8 +1702,8 @@
       <c r="Q42" s="8"/>
     </row>
     <row r="43" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="28"/>
-      <c r="C43" s="29"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="36"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -1719,10 +1720,10 @@
       <c r="Q43" s="8"/>
     </row>
     <row r="44" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="27"/>
+      <c r="C44" s="34"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -1739,8 +1740,8 @@
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="28"/>
-      <c r="C45" s="29"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="36"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -1757,10 +1758,10 @@
       <c r="Q45" s="8"/>
     </row>
     <row r="46" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C46" s="19"/>
+      <c r="C46" s="12"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -1777,8 +1778,8 @@
       <c r="Q46" s="8"/>
     </row>
     <row r="47" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="20"/>
-      <c r="C47" s="21"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -1795,10 +1796,10 @@
       <c r="Q47" s="1"/>
     </row>
     <row r="48" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="19"/>
+      <c r="C48" s="12"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -1814,8 +1815,8 @@
       <c r="Q48" s="1"/>
     </row>
     <row r="49" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="20"/>
-      <c r="C49" s="21"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -1832,10 +1833,10 @@
       <c r="Q49" s="1"/>
     </row>
     <row r="50" spans="2:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C50" s="19"/>
+      <c r="C50" s="12"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -1852,8 +1853,8 @@
       <c r="Q50" s="1"/>
     </row>
     <row r="51" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="20"/>
-      <c r="C51" s="21"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -1870,10 +1871,10 @@
       <c r="Q51" s="1"/>
     </row>
     <row r="52" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="13"/>
+      <c r="C52" s="50"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
@@ -1890,10 +1891,10 @@
       <c r="Q52" s="8"/>
     </row>
     <row r="53" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C53" s="19"/>
+      <c r="C53" s="12"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
@@ -1910,8 +1911,8 @@
       <c r="Q53" s="8"/>
     </row>
     <row r="54" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="20"/>
-      <c r="C54" s="21"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="14"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
@@ -1928,10 +1929,10 @@
       <c r="Q54" s="8"/>
     </row>
     <row r="55" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="19"/>
+      <c r="C55" s="12"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
@@ -1948,8 +1949,8 @@
       <c r="Q55" s="8"/>
     </row>
     <row r="56" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="20"/>
-      <c r="C56" s="21"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="14"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
@@ -1966,10 +1967,10 @@
       <c r="Q56" s="8"/>
     </row>
     <row r="57" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="C57" s="13"/>
+      <c r="C57" s="50"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -1986,10 +1987,10 @@
       <c r="Q57" s="8"/>
     </row>
     <row r="58" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C58" s="15"/>
+      <c r="C58" s="30"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
@@ -2006,8 +2007,8 @@
       <c r="Q58" s="8"/>
     </row>
     <row r="59" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="16"/>
-      <c r="C59" s="17"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="32"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
@@ -2024,10 +2025,10 @@
       <c r="Q59" s="8"/>
     </row>
     <row r="60" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="19"/>
+      <c r="C60" s="12"/>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
@@ -2044,8 +2045,8 @@
       <c r="Q60" s="8"/>
     </row>
     <row r="61" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="20"/>
-      <c r="C61" s="21"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="14"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
@@ -2062,10 +2063,10 @@
       <c r="Q61" s="8"/>
     </row>
     <row r="62" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C62" s="15"/>
+      <c r="C62" s="30"/>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="7"/>
@@ -2082,8 +2083,8 @@
       <c r="Q62" s="8"/>
     </row>
     <row r="63" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="16"/>
-      <c r="C63" s="17"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="32"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -2100,10 +2101,10 @@
       <c r="Q63" s="1"/>
     </row>
     <row r="64" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="15"/>
+      <c r="C64" s="30"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -2120,8 +2121,8 @@
       <c r="Q64" s="1"/>
     </row>
     <row r="65" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="16"/>
-      <c r="C65" s="17"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="32"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -2138,10 +2139,10 @@
       <c r="Q65" s="1"/>
     </row>
     <row r="66" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="18" t="s">
+      <c r="B66" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="19"/>
+      <c r="C66" s="12"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -2158,8 +2159,8 @@
       <c r="Q66" s="1"/>
     </row>
     <row r="67" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="20"/>
-      <c r="C67" s="21"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="14"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -2176,10 +2177,10 @@
       <c r="Q67" s="1"/>
     </row>
     <row r="68" spans="2:17" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="45" t="s">
+      <c r="B68" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C68" s="44"/>
+      <c r="C68" s="27"/>
       <c r="D68" s="22"/>
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
@@ -2189,15 +2190,15 @@
       <c r="J68" s="22"/>
       <c r="K68" s="22"/>
       <c r="L68" s="22"/>
-      <c r="M68" s="39"/>
-      <c r="N68" s="39"/>
+      <c r="M68" s="20"/>
+      <c r="N68" s="20"/>
       <c r="O68" s="22"/>
       <c r="P68" s="22"/>
       <c r="Q68" s="22"/>
     </row>
     <row r="69" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="44"/>
-      <c r="C69" s="44"/>
+      <c r="B69" s="27"/>
+      <c r="C69" s="27"/>
       <c r="D69" s="23"/>
       <c r="E69" s="23"/>
       <c r="F69" s="23"/>
@@ -2207,15 +2208,15 @@
       <c r="J69" s="23"/>
       <c r="K69" s="23"/>
       <c r="L69" s="23"/>
-      <c r="M69" s="40"/>
-      <c r="N69" s="40"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
       <c r="O69" s="23"/>
       <c r="P69" s="23"/>
       <c r="Q69" s="23"/>
     </row>
     <row r="70" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="44"/>
-      <c r="C70" s="44"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="27"/>
       <c r="D70" s="22"/>
       <c r="E70" s="22"/>
       <c r="F70" s="22"/>
@@ -2232,8 +2233,8 @@
       <c r="Q70" s="22"/>
     </row>
     <row r="71" spans="2:17" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
+      <c r="B71" s="27"/>
+      <c r="C71" s="27"/>
       <c r="D71" s="23"/>
       <c r="E71" s="23"/>
       <c r="F71" s="23"/>
@@ -2250,10 +2251,10 @@
       <c r="Q71" s="23"/>
     </row>
     <row r="72" spans="2:17" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="19"/>
+      <c r="C72" s="12"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="8"/>
@@ -2269,8 +2270,8 @@
       <c r="Q72" s="8"/>
     </row>
     <row r="73" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="20"/>
-      <c r="C73" s="21"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="14"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -2287,10 +2288,10 @@
       <c r="Q73" s="1"/>
     </row>
     <row r="74" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="19"/>
+      <c r="C74" s="12"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -2305,8 +2306,8 @@
       <c r="Q74" s="1"/>
     </row>
     <row r="75" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="20"/>
-      <c r="C75" s="21"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="14"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -2323,10 +2324,10 @@
       <c r="Q75" s="1"/>
     </row>
     <row r="76" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="18" t="s">
+      <c r="B76" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="19"/>
+      <c r="C76" s="12"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
@@ -2343,8 +2344,8 @@
       <c r="Q76" s="1"/>
     </row>
     <row r="77" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="20"/>
-      <c r="C77" s="21"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="14"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -2361,10 +2362,10 @@
       <c r="Q77" s="1"/>
     </row>
     <row r="78" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="18" t="s">
+      <c r="B78" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C78" s="19"/>
+      <c r="C78" s="12"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
@@ -2376,13 +2377,13 @@
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
-      <c r="P78" s="9"/>
+      <c r="O78" s="9"/>
+      <c r="P78" s="53"/>
       <c r="Q78" s="8"/>
     </row>
     <row r="79" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="20"/>
-      <c r="C79" s="21"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="14"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -2399,10 +2400,10 @@
       <c r="Q79" s="1"/>
     </row>
     <row r="80" spans="2:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="18" t="s">
+      <c r="B80" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C80" s="19"/>
+      <c r="C80" s="12"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -2414,13 +2415,13 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
-      <c r="O80" s="1"/>
-      <c r="P80" s="9"/>
+      <c r="O80" s="9"/>
+      <c r="P80" s="53"/>
       <c r="Q80" s="1"/>
     </row>
     <row r="81" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="20"/>
-      <c r="C81" s="21"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="14"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -2437,10 +2438,10 @@
       <c r="Q81" s="1"/>
     </row>
     <row r="82" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="49" t="s">
+      <c r="B82" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C82" s="50"/>
+      <c r="C82" s="45"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -2452,13 +2453,13 @@
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
+      <c r="O82" s="9"/>
       <c r="P82" s="1"/>
-      <c r="Q82" s="9"/>
+      <c r="Q82" s="53"/>
     </row>
     <row r="83" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="51"/>
-      <c r="C83" s="52"/>
+      <c r="B83" s="46"/>
+      <c r="C83" s="47"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -2497,15 +2498,15 @@
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="30" t="s">
+      <c r="F85" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="G85" s="31"/>
-      <c r="H85" s="41"/>
-      <c r="I85" s="41"/>
-      <c r="J85" s="43"/>
-      <c r="K85" s="43"/>
-      <c r="L85" s="43"/>
+      <c r="G85" s="43"/>
+      <c r="H85" s="24"/>
+      <c r="I85" s="24"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="25"/>
+      <c r="L85" s="25"/>
       <c r="M85" s="6"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -2517,15 +2518,15 @@
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="30" t="s">
+      <c r="F86" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="G86" s="31"/>
-      <c r="H86" s="42"/>
-      <c r="I86" s="42"/>
-      <c r="J86" s="43"/>
-      <c r="K86" s="43"/>
-      <c r="L86" s="43"/>
+      <c r="G86" s="43"/>
+      <c r="H86" s="15"/>
+      <c r="I86" s="15"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="25"/>
+      <c r="L86" s="25"/>
       <c r="M86" s="6"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -2534,44 +2535,54 @@
     </row>
   </sheetData>
   <mergeCells count="111">
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="B8:C9"/>
-    <mergeCell ref="N68:N69"/>
-    <mergeCell ref="O68:O69"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="J85:L85"/>
-    <mergeCell ref="J86:L86"/>
-    <mergeCell ref="B68:C71"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="L34:L35"/>
-    <mergeCell ref="K34:K35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="B48:C49"/>
-    <mergeCell ref="B50:C51"/>
-    <mergeCell ref="B62:C63"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="B66:C67"/>
+    <mergeCell ref="B1:Q1"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C59"/>
+    <mergeCell ref="B60:C61"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C54"/>
+    <mergeCell ref="B55:C56"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="K68:K69"/>
+    <mergeCell ref="K70:K71"/>
+    <mergeCell ref="O70:O71"/>
+    <mergeCell ref="P68:P69"/>
+    <mergeCell ref="P70:P71"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="B78:C79"/>
+    <mergeCell ref="B80:C81"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="B72:C73"/>
+    <mergeCell ref="B74:C75"/>
+    <mergeCell ref="B76:C77"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B82:C83"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:O23"/>
     <mergeCell ref="P22:P23"/>
     <mergeCell ref="Q22:Q23"/>
     <mergeCell ref="B42:C43"/>
@@ -2596,55 +2607,45 @@
     <mergeCell ref="O34:O35"/>
     <mergeCell ref="N34:N35"/>
     <mergeCell ref="M68:M69"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="N68:N69"/>
+    <mergeCell ref="O68:O69"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="J85:L85"/>
+    <mergeCell ref="J86:L86"/>
+    <mergeCell ref="B68:C71"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="B48:C49"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="B62:C63"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="B66:C67"/>
     <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B78:C79"/>
-    <mergeCell ref="B80:C81"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="B72:C73"/>
-    <mergeCell ref="B74:C75"/>
-    <mergeCell ref="B76:C77"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B82:C83"/>
-    <mergeCell ref="B1:Q1"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C59"/>
-    <mergeCell ref="B60:C61"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C54"/>
-    <mergeCell ref="B55:C56"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="J68:J69"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="K68:K69"/>
-    <mergeCell ref="K70:K71"/>
-    <mergeCell ref="O70:O71"/>
-    <mergeCell ref="P68:P69"/>
-    <mergeCell ref="P70:P71"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="B24:C25"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="B8:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="34" orientation="landscape" r:id="rId1"/>

--- a/Organizacion_Proyecto/Calendario_actividades/Calendario de actividades.xlsx
+++ b/Organizacion_Proyecto/Calendario_actividades/Calendario de actividades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elies\Documents\GitHub\integradoraTeampoderoso\Organizacion_Proyecto\Calendario_actividades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2899B3-2E19-49B5-A43C-8E9B4ACBA959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAC9F95-FA38-449A-BFB9-4E5B2088BC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30A5C19A-5DFA-4927-AC28-1A5B7C8ACF0F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
   <si>
     <t>ACTIVIDADES</t>
   </si>
@@ -135,12 +135,6 @@
     <t>4.4.2 PRUEBAS DE ACCESO</t>
   </si>
   <si>
-    <t>4.4.3 PRUEBAS DE ACCESO</t>
-  </si>
-  <si>
-    <t>4.4.4 CONSULTAS ESPECÍFICAS</t>
-  </si>
-  <si>
     <t xml:space="preserve">CAPÍTULO IV MÉTODOLOGÍA DE APLICACIÓN </t>
   </si>
   <si>
@@ -190,6 +184,9 @@
   </si>
   <si>
     <t>INTEGRANTES: REYNA ITZEL DIEGO ESTRADA, ELI ESPINOZA TREVIÑO, LEVI BRAYAN MUNDO ESCAMILLA, ISRRAEL REYES OLMOS</t>
+  </si>
+  <si>
+    <t>4.4.3 CONSULTAS ESPECÍFICAS</t>
   </si>
 </sst>
 </file>
@@ -381,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -401,6 +398,28 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -413,9 +432,84 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -425,109 +519,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -845,7 +844,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q86"/>
+  <dimension ref="B1:Q84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
@@ -862,76 +861,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
+      <c r="B1" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
     </row>
     <row r="2" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="17">
+      <c r="B2" s="50">
         <v>2025</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
     </row>
     <row r="3" spans="2:17" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16" t="s">
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="16"/>
+      <c r="Q3" s="49"/>
     </row>
     <row r="4" spans="2:17" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
@@ -976,10 +975,10 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="19"/>
+      <c r="B5" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="42"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -996,10 +995,10 @@
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="12"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="9"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1016,8 +1015,8 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="1"/>
@@ -1034,10 +1033,10 @@
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="1"/>
       <c r="E8" s="9"/>
       <c r="F8" s="1"/>
@@ -1054,8 +1053,8 @@
       <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="1"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -1072,10 +1071,10 @@
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="12"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="1"/>
       <c r="E10" s="9"/>
       <c r="F10" s="1"/>
@@ -1092,11 +1091,11 @@
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1110,10 +1109,10 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="1"/>
       <c r="E12" s="9"/>
       <c r="F12" s="1"/>
@@ -1130,8 +1129,8 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="1"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -1148,10 +1147,10 @@
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="12"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="1"/>
       <c r="E14" s="9"/>
       <c r="F14" s="1"/>
@@ -1168,8 +1167,8 @@
       <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="1"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -1186,10 +1185,10 @@
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="12"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="9"/>
@@ -1206,8 +1205,8 @@
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="10"/>
@@ -1224,10 +1223,10 @@
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="12"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="9"/>
@@ -1244,8 +1243,8 @@
       <c r="Q18" s="1"/>
     </row>
     <row r="19" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="10"/>
@@ -1262,10 +1261,10 @@
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C20" s="20"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1282,8 +1281,8 @@
       <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1300,48 +1299,48 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
+      <c r="B22" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="42"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
     </row>
     <row r="23" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="12"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="9"/>
@@ -1358,8 +1357,8 @@
       <c r="Q24" s="4"/>
     </row>
     <row r="25" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="22"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="10"/>
@@ -1376,10 +1375,10 @@
       <c r="Q25" s="1"/>
     </row>
     <row r="26" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="12"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="9"/>
@@ -1396,8 +1395,8 @@
       <c r="Q26" s="1"/>
     </row>
     <row r="27" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="10"/>
@@ -1414,10 +1413,10 @@
       <c r="Q27" s="1"/>
     </row>
     <row r="28" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="12"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="9"/>
@@ -1434,8 +1433,8 @@
       <c r="Q28" s="1"/>
     </row>
     <row r="29" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="10"/>
@@ -1452,10 +1451,10 @@
       <c r="Q29" s="1"/>
     </row>
     <row r="30" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="39"/>
+      <c r="C30" s="38"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="9"/>
@@ -1472,8 +1471,8 @@
       <c r="Q30" s="1"/>
     </row>
     <row r="31" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="10"/>
@@ -1490,10 +1489,10 @@
       <c r="Q31" s="1"/>
     </row>
     <row r="32" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="39"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="9"/>
@@ -1510,8 +1509,8 @@
       <c r="Q32" s="1"/>
     </row>
     <row r="33" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="10"/>
@@ -1528,48 +1527,48 @@
       <c r="Q33" s="1"/>
     </row>
     <row r="34" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="43"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
     </row>
     <row r="35" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="43"/>
+      <c r="Q35" s="43"/>
     </row>
     <row r="36" spans="2:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="19"/>
+      <c r="B36" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="42"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -1586,10 +1585,10 @@
       <c r="Q36" s="1"/>
     </row>
     <row r="37" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="12"/>
+      <c r="C37" s="20"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -1606,8 +1605,8 @@
       <c r="Q37" s="1"/>
     </row>
     <row r="38" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -1624,10 +1623,10 @@
       <c r="Q38" s="1"/>
     </row>
     <row r="39" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="52"/>
+      <c r="B39" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="26"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -1644,10 +1643,10 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="34"/>
+      <c r="B40" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="28"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -1664,8 +1663,8 @@
       <c r="Q40" s="8"/>
     </row>
     <row r="41" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="35"/>
-      <c r="C41" s="36"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="30"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -1682,10 +1681,10 @@
       <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="34"/>
+      <c r="B42" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="28"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -1702,8 +1701,8 @@
       <c r="Q42" s="8"/>
     </row>
     <row r="43" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="35"/>
-      <c r="C43" s="36"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="30"/>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -1720,10 +1719,10 @@
       <c r="Q43" s="8"/>
     </row>
     <row r="44" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C44" s="34"/>
+      <c r="B44" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="28"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -1740,8 +1739,8 @@
       <c r="Q44" s="8"/>
     </row>
     <row r="45" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="35"/>
-      <c r="C45" s="36"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="30"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
@@ -1758,10 +1757,10 @@
       <c r="Q45" s="8"/>
     </row>
     <row r="46" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C46" s="12"/>
+      <c r="C46" s="20"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -1778,8 +1777,8 @@
       <c r="Q46" s="8"/>
     </row>
     <row r="47" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="13"/>
-      <c r="C47" s="14"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="22"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -1796,10 +1795,10 @@
       <c r="Q47" s="1"/>
     </row>
     <row r="48" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="12"/>
+      <c r="C48" s="20"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -1815,8 +1814,8 @@
       <c r="Q48" s="1"/>
     </row>
     <row r="49" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="13"/>
-      <c r="C49" s="14"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -1833,10 +1832,10 @@
       <c r="Q49" s="1"/>
     </row>
     <row r="50" spans="2:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C50" s="12"/>
+      <c r="C50" s="20"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -1853,16 +1852,16 @@
       <c r="Q50" s="1"/>
     </row>
     <row r="51" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="13"/>
-      <c r="C51" s="14"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
@@ -1871,10 +1870,10 @@
       <c r="Q51" s="1"/>
     </row>
     <row r="52" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="50"/>
+      <c r="B52" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="14"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
@@ -1891,18 +1890,18 @@
       <c r="Q52" s="8"/>
     </row>
     <row r="53" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C53" s="12"/>
+      <c r="B53" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="20"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="9"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
@@ -1911,16 +1910,16 @@
       <c r="Q53" s="8"/>
     </row>
     <row r="54" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="13"/>
-      <c r="C54" s="14"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="22"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="8"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="53"/>
+      <c r="K54" s="53"/>
       <c r="L54" s="8"/>
       <c r="M54" s="8"/>
       <c r="N54" s="8"/>
@@ -1929,18 +1928,18 @@
       <c r="Q54" s="8"/>
     </row>
     <row r="55" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C55" s="12"/>
+      <c r="B55" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55" s="20"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="9"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
       <c r="L55" s="8"/>
       <c r="M55" s="8"/>
       <c r="N55" s="8"/>
@@ -1949,16 +1948,16 @@
       <c r="Q55" s="8"/>
     </row>
     <row r="56" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="13"/>
-      <c r="C56" s="14"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="22"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="8"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="53"/>
+      <c r="K56" s="53"/>
       <c r="L56" s="8"/>
       <c r="M56" s="8"/>
       <c r="N56" s="8"/>
@@ -1967,10 +1966,10 @@
       <c r="Q56" s="8"/>
     </row>
     <row r="57" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="C57" s="50"/>
+      <c r="B57" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="14"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -1987,10 +1986,10 @@
       <c r="Q57" s="8"/>
     </row>
     <row r="58" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C58" s="30"/>
+      <c r="B58" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" s="16"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
@@ -2007,15 +2006,15 @@
       <c r="Q58" s="8"/>
     </row>
     <row r="59" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="31"/>
-      <c r="C59" s="32"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="18"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
+      <c r="J59" s="53"/>
       <c r="K59" s="1"/>
       <c r="L59" s="8"/>
       <c r="M59" s="8"/>
@@ -2025,10 +2024,10 @@
       <c r="Q59" s="8"/>
     </row>
     <row r="60" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C60" s="12"/>
+      <c r="B60" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="20"/>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
@@ -2045,8 +2044,8 @@
       <c r="Q60" s="8"/>
     </row>
     <row r="61" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="13"/>
-      <c r="C61" s="14"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="22"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
@@ -2054,7 +2053,7 @@
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
-      <c r="K61" s="1"/>
+      <c r="K61" s="52"/>
       <c r="L61" s="1"/>
       <c r="M61" s="8"/>
       <c r="N61" s="8"/>
@@ -2063,10 +2062,10 @@
       <c r="Q61" s="8"/>
     </row>
     <row r="62" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="29" t="s">
+      <c r="B62" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C62" s="30"/>
+      <c r="C62" s="16"/>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="7"/>
@@ -2075,7 +2074,7 @@
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
       <c r="K62" s="8"/>
-      <c r="L62" s="9"/>
+      <c r="L62" s="11"/>
       <c r="M62" s="8"/>
       <c r="N62" s="8"/>
       <c r="O62" s="8"/>
@@ -2083,8 +2082,8 @@
       <c r="Q62" s="8"/>
     </row>
     <row r="63" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="31"/>
-      <c r="C63" s="32"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="18"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -2101,10 +2100,10 @@
       <c r="Q63" s="1"/>
     </row>
     <row r="64" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="29" t="s">
+      <c r="B64" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="30"/>
+      <c r="C64" s="16"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -2121,8 +2120,8 @@
       <c r="Q64" s="1"/>
     </row>
     <row r="65" spans="2:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="31"/>
-      <c r="C65" s="32"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="18"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -2139,10 +2138,10 @@
       <c r="Q65" s="1"/>
     </row>
     <row r="66" spans="2:17" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="12"/>
+      <c r="C66" s="20"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -2159,8 +2158,8 @@
       <c r="Q66" s="1"/>
     </row>
     <row r="67" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="13"/>
-      <c r="C67" s="14"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="22"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -2177,84 +2176,84 @@
       <c r="Q67" s="1"/>
     </row>
     <row r="68" spans="2:17" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="26" t="s">
+      <c r="B68" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C68" s="27"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
-      <c r="L68" s="22"/>
-      <c r="M68" s="20"/>
-      <c r="N68" s="20"/>
-      <c r="O68" s="22"/>
-      <c r="P68" s="22"/>
-      <c r="Q68" s="22"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="23"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="23"/>
+      <c r="K68" s="23"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="54"/>
+      <c r="N68" s="54"/>
+      <c r="O68" s="23"/>
+      <c r="P68" s="23"/>
+      <c r="Q68" s="23"/>
     </row>
     <row r="69" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="23"/>
-      <c r="I69" s="23"/>
-      <c r="J69" s="23"/>
-      <c r="K69" s="23"/>
-      <c r="L69" s="23"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="23"/>
-      <c r="P69" s="23"/>
-      <c r="Q69" s="23"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="55"/>
+      <c r="N69" s="55"/>
+      <c r="O69" s="24"/>
+      <c r="P69" s="24"/>
+      <c r="Q69" s="24"/>
     </row>
     <row r="70" spans="2:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
-      <c r="K70" s="22"/>
-      <c r="L70" s="22"/>
-      <c r="M70" s="22"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="22"/>
-      <c r="P70" s="22"/>
-      <c r="Q70" s="22"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="23"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="23"/>
+      <c r="H70" s="23"/>
+      <c r="I70" s="23"/>
+      <c r="J70" s="23"/>
+      <c r="K70" s="23"/>
+      <c r="L70" s="23"/>
+      <c r="M70" s="23"/>
+      <c r="N70" s="23"/>
+      <c r="O70" s="23"/>
+      <c r="P70" s="23"/>
+      <c r="Q70" s="23"/>
     </row>
     <row r="71" spans="2:17" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
-      <c r="J71" s="23"/>
-      <c r="K71" s="23"/>
-      <c r="L71" s="23"/>
-      <c r="M71" s="23"/>
-      <c r="N71" s="23"/>
-      <c r="O71" s="23"/>
-      <c r="P71" s="23"/>
-      <c r="Q71" s="23"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24"/>
+      <c r="I71" s="24"/>
+      <c r="J71" s="24"/>
+      <c r="K71" s="24"/>
+      <c r="L71" s="24"/>
+      <c r="M71" s="24"/>
+      <c r="N71" s="24"/>
+      <c r="O71" s="24"/>
+      <c r="P71" s="24"/>
+      <c r="Q71" s="24"/>
     </row>
     <row r="72" spans="2:17" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="12"/>
+      <c r="C72" s="20"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="8"/>
@@ -2270,8 +2269,8 @@
       <c r="Q72" s="8"/>
     </row>
     <row r="73" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="13"/>
-      <c r="C73" s="14"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="22"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -2288,10 +2287,10 @@
       <c r="Q73" s="1"/>
     </row>
     <row r="74" spans="2:17" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="12"/>
+      <c r="C74" s="20"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -2306,8 +2305,8 @@
       <c r="Q74" s="1"/>
     </row>
     <row r="75" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="13"/>
-      <c r="C75" s="14"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="22"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -2324,10 +2323,10 @@
       <c r="Q75" s="1"/>
     </row>
     <row r="76" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="12"/>
+      <c r="C76" s="20"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
@@ -2344,8 +2343,8 @@
       <c r="Q76" s="1"/>
     </row>
     <row r="77" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="13"/>
-      <c r="C77" s="14"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="22"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -2361,11 +2360,11 @@
       <c r="P77" s="1"/>
       <c r="Q77" s="1"/>
     </row>
-    <row r="78" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C78" s="12"/>
+    <row r="78" spans="2:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78" s="20"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
@@ -2378,12 +2377,12 @@
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="9"/>
-      <c r="P78" s="53"/>
-      <c r="Q78" s="8"/>
-    </row>
-    <row r="79" spans="2:17" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="13"/>
-      <c r="C79" s="14"/>
+      <c r="P78" s="11"/>
+      <c r="Q78" s="1"/>
+    </row>
+    <row r="79" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="21"/>
+      <c r="C79" s="22"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -2399,11 +2398,11 @@
       <c r="P79" s="1"/>
       <c r="Q79" s="1"/>
     </row>
-    <row r="80" spans="2:17" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="11" t="s">
+    <row r="80" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="C80" s="12"/>
+      <c r="C80" s="34"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -2416,12 +2415,12 @@
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="9"/>
-      <c r="P80" s="53"/>
-      <c r="Q80" s="1"/>
-    </row>
-    <row r="81" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="13"/>
-      <c r="C81" s="14"/>
+      <c r="P80" s="1"/>
+      <c r="Q80" s="11"/>
+    </row>
+    <row r="81" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="35"/>
+      <c r="C81" s="36"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -2437,104 +2436,152 @@
       <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
     </row>
-    <row r="82" spans="2:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C82" s="45"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="9"/>
-      <c r="P82" s="1"/>
-      <c r="Q82" s="53"/>
-    </row>
-    <row r="83" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="46"/>
-      <c r="C83" s="47"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
-      <c r="M83" s="1"/>
-      <c r="N83" s="1"/>
-      <c r="O83" s="1"/>
-      <c r="P83" s="1"/>
-      <c r="Q83" s="1"/>
-    </row>
-    <row r="84" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
+    </row>
+    <row r="83" spans="2:17" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="G83" s="32"/>
+      <c r="H83" s="44"/>
+      <c r="I83" s="44"/>
+      <c r="J83" s="46"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="2"/>
+    </row>
+    <row r="84" spans="2:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
+      <c r="F84" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G84" s="32"/>
+      <c r="H84" s="45"/>
+      <c r="I84" s="45"/>
+      <c r="J84" s="46"/>
+      <c r="K84" s="46"/>
+      <c r="L84" s="46"/>
+      <c r="M84" s="6"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
     </row>
-    <row r="85" spans="2:17" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="G85" s="43"/>
-      <c r="H85" s="24"/>
-      <c r="I85" s="24"/>
-      <c r="J85" s="25"/>
-      <c r="K85" s="25"/>
-      <c r="L85" s="25"/>
-      <c r="M85" s="6"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" s="2"/>
-      <c r="Q85" s="2"/>
-    </row>
-    <row r="86" spans="2:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="G86" s="43"/>
-      <c r="H86" s="15"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="25"/>
-      <c r="K86" s="25"/>
-      <c r="L86" s="25"/>
-      <c r="M86" s="6"/>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" s="2"/>
-      <c r="Q86" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="111">
+  <mergeCells count="110">
+    <mergeCell ref="B10:C11"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="B8:C9"/>
+    <mergeCell ref="N68:N69"/>
+    <mergeCell ref="O68:O69"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="J84:L84"/>
+    <mergeCell ref="B68:C71"/>
+    <mergeCell ref="M34:M35"/>
+    <mergeCell ref="L34:L35"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="B48:C49"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="B62:C63"/>
+    <mergeCell ref="B64:C65"/>
+    <mergeCell ref="B66:C67"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="P22:P23"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="Q68:Q69"/>
+    <mergeCell ref="Q70:Q71"/>
+    <mergeCell ref="L68:L69"/>
+    <mergeCell ref="L70:L71"/>
+    <mergeCell ref="M70:M71"/>
+    <mergeCell ref="N70:N71"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="B22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="Q34:Q35"/>
+    <mergeCell ref="P34:P35"/>
+    <mergeCell ref="O34:O35"/>
+    <mergeCell ref="N34:N35"/>
+    <mergeCell ref="M68:M69"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="M22:M23"/>
+    <mergeCell ref="N22:N23"/>
+    <mergeCell ref="O22:O23"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="B78:C79"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="G68:G69"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="B72:C73"/>
+    <mergeCell ref="B74:C75"/>
+    <mergeCell ref="B76:C77"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="B80:C81"/>
     <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B58:C59"/>
@@ -2559,93 +2606,6 @@
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="B26:C27"/>
     <mergeCell ref="B28:C29"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="B78:C79"/>
-    <mergeCell ref="B80:C81"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="B72:C73"/>
-    <mergeCell ref="B74:C75"/>
-    <mergeCell ref="B76:C77"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="B82:C83"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="B46:C47"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="M22:M23"/>
-    <mergeCell ref="N22:N23"/>
-    <mergeCell ref="O22:O23"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="Q22:Q23"/>
-    <mergeCell ref="B42:C43"/>
-    <mergeCell ref="B44:C45"/>
-    <mergeCell ref="Q68:Q69"/>
-    <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="L68:L69"/>
-    <mergeCell ref="L70:L71"/>
-    <mergeCell ref="M70:M71"/>
-    <mergeCell ref="N70:N71"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="B22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="Q34:Q35"/>
-    <mergeCell ref="P34:P35"/>
-    <mergeCell ref="O34:O35"/>
-    <mergeCell ref="N34:N35"/>
-    <mergeCell ref="M68:M69"/>
-    <mergeCell ref="N68:N69"/>
-    <mergeCell ref="O68:O69"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="J85:L85"/>
-    <mergeCell ref="J86:L86"/>
-    <mergeCell ref="B68:C71"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="L34:L35"/>
-    <mergeCell ref="K34:K35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="B48:C49"/>
-    <mergeCell ref="B50:C51"/>
-    <mergeCell ref="B62:C63"/>
-    <mergeCell ref="B64:C65"/>
-    <mergeCell ref="B66:C67"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="B10:C11"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="B14:C15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="B2:Q2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="B8:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" scale="34" orientation="landscape" r:id="rId1"/>
